--- a/Estoque_Empregos_RAIS_Ananindeua_Capanema.xlsx
+++ b/Estoque_Empregos_RAIS_Ananindeua_Capanema.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,13 +34,47 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A5E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2A5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +89,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,127 +471,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ESTOQUE DE EMPREGOS FORMAIS POR SEÇÃO CNAE — ANANINDEUA — 2001 A 2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Vínculos empregatícios ativos em 31/12. Fonte: RAIS/MTE — microdados de vínculos (2001-2005: CNAE 95 convertido via tabela de correspondência oficial IBGE; 2007+: CNAE 2.0 direto).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2001</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2003</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2005</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2007</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2009</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2011</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2013</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2015</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2017</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2019</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2021</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2023</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2025</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Δ% acum.
 2001→2025</t>
@@ -556,1233 +599,1238 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>1876</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="7" t="n">
         <v>1506</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7" t="n">
         <v>1522</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="7" t="n">
         <v>1334</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="7" t="n">
         <v>1715</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="7" t="n">
         <v>1990</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="7" t="n">
         <v>2144</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="7" t="n">
         <v>2286</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="7" t="n">
         <v>181</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>-5.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="9" t="n">
         <v>96</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>160</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>-61.5%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>6174</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>7517</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>8592</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>5535</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="7" t="n">
         <v>4902</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="7" t="n">
         <v>5454</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="7" t="n">
         <v>5291</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="7" t="n">
         <v>5383</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="7" t="n">
         <v>5330</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="7" t="n">
         <v>5946</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="7" t="n">
         <v>6521</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="7" t="n">
         <v>8729</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="7" t="n">
         <v>9889</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>60.2%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>142</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="9" t="n">
         <v>152</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="L7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="7" t="n">
         <v>249</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="7" t="n">
         <v>126</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="7" t="n">
         <v>325</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="7" t="n">
         <v>446</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="7" t="n">
         <v>563</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="7" t="n">
         <v>583</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="7" t="n">
         <v>1555</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="7" t="n">
         <v>1460</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>3845.9%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>2056</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="9" t="n">
         <v>2163</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="9" t="n">
         <v>2795</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>4621</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="9" t="n">
         <v>5775</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>7692</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="9" t="n">
         <v>6616</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="9" t="n">
         <v>7046</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="9" t="n">
         <v>7388</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="9" t="n">
         <v>5530</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="9" t="n">
         <v>4956</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="9" t="n">
         <v>6845</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="9" t="n">
         <v>5365</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>160.9%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>7415</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>10376</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>13460</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>14277</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>14786</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>17373</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>18382</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="7" t="n">
         <v>18780</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="7" t="n">
         <v>18207</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="7" t="n">
         <v>17599</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="7" t="n">
         <v>20723</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="7" t="n">
         <v>22298</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="7" t="n">
         <v>23853</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>221.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="9" t="n">
         <v>4418</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="9" t="n">
         <v>4814</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="9" t="n">
         <v>5331</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>5231</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="9" t="n">
         <v>5270</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="9" t="n">
         <v>6493</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="9" t="n">
         <v>6571</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="9" t="n">
         <v>7691</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="9" t="n">
         <v>6630</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="9" t="n">
         <v>6074</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="9" t="n">
         <v>5855</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="9" t="n">
         <v>6645</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="9" t="n">
         <v>6576</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>48.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>401</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>936</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>1093</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>1516</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>1511</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>1961</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>1322</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="7" t="n">
         <v>1338</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="7" t="n">
         <v>1577</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="7" t="n">
         <v>1620</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="7" t="n">
         <v>1900</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="7" t="n">
         <v>2563</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="7" t="n">
         <v>2767</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>590.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="9" t="n">
         <v>223</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="9" t="n">
         <v>259</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="9" t="n">
         <v>240</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="9" t="n">
         <v>536</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="9" t="n">
         <v>568</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="9" t="inlineStr">
         <is>
           <t>3957.1%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>180</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>271</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>247</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>344</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="7" t="n">
         <v>351</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="7" t="n">
         <v>393</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="7" t="n">
         <v>376</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="7" t="n">
         <v>394</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="7" t="n">
         <v>1079</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="7" t="n">
         <v>1026</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="7" t="n">
         <v>1352</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="7" t="n">
         <v>1329</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>638.3%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="9" t="n">
         <v>76</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="9" t="n">
         <v>180</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="9" t="n">
         <v>298</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="9" t="n">
         <v>369</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>5171.4%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="7" t="n">
         <v>156</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="7" t="n">
         <v>514</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="7" t="n">
         <v>583</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="7" t="n">
         <v>671</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="7" t="n">
         <v>816</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="7" t="n">
         <v>533</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="7" t="n">
         <v>683</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="7" t="n">
         <v>625</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="7" t="n">
         <v>772</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="7" t="n">
         <v>1151</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="7" t="n">
         <v>1541</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="7" t="n">
         <v>1683</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>945.3%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="9" t="n">
         <v>1040</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="9" t="n">
         <v>3855</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="9" t="n">
         <v>4655</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="9" t="n">
         <v>4454</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="9" t="n">
         <v>3154</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="9" t="n">
         <v>3835</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="9" t="n">
         <v>5791</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="9" t="n">
         <v>6030</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="9" t="n">
         <v>4824</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="9" t="n">
         <v>7942</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="9" t="n">
         <v>9104</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="9" t="n">
         <v>9786</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="9" t="n">
         <v>11443</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>1000.3%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>3391</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="7" t="n">
         <v>3382</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="7" t="n">
         <v>6299</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="7" t="n">
         <v>4457</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="7" t="n">
         <v>7530</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="7" t="n">
         <v>9138</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="7" t="n">
         <v>10318</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="7" t="n">
         <v>10905</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="7" t="n">
         <v>9869</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="7" t="n">
         <v>5498</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="7" t="n">
         <v>5078</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="7" t="n">
         <v>6107</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="7" t="n">
         <v>7211</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>112.7%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>876</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="9" t="n">
         <v>1051</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="9" t="n">
         <v>1322</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="9" t="n">
         <v>1513</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="9" t="n">
         <v>1838</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="9" t="n">
         <v>1996</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="9" t="n">
         <v>2265</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="9" t="n">
         <v>2588</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="9" t="n">
         <v>6932</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="9" t="n">
         <v>6229</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="9" t="n">
         <v>9650</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="9" t="n">
         <v>12833</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="9" t="inlineStr">
         <is>
           <t>1365.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="7" t="n">
         <v>576</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="7" t="n">
         <v>571</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="7" t="n">
         <v>1834</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="7" t="n">
         <v>1957</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="7" t="n">
         <v>2083</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="7" t="n">
         <v>2073</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="7" t="n">
         <v>2515</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="7" t="n">
         <v>2777</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="7" t="n">
         <v>3172</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="7" t="n">
         <v>3658</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="7" t="n">
         <v>3202</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="7" t="n">
         <v>3327</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>477.6%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="9" t="n">
         <v>115</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="9" t="n">
         <v>131</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="9" t="n">
         <v>141</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="9" t="n">
         <v>256</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="9" t="n">
         <v>260</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="9" t="n">
         <v>290</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="9" t="n">
         <v>445</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="9" t="n">
         <v>575</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="9" t="inlineStr">
         <is>
           <t>568.6%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>609</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="7" t="n">
         <v>675</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="7" t="n">
         <v>756</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="7" t="n">
         <v>518</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
         <v>544</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="7" t="n">
         <v>579</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="7" t="n">
         <v>627</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="7" t="n">
         <v>616</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="7" t="n">
         <v>844</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="7" t="n">
         <v>895</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="7" t="n">
         <v>1049</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="7" t="n">
         <v>849</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="7" t="n">
         <v>1050</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>72.4%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
         <is>
           <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>26862</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="9" t="n">
         <v>36088</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="9" t="n">
         <v>45955</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="9" t="n">
         <v>47204</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="9" t="n">
         <v>50192</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="9" t="n">
         <v>59748</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="9" t="n">
         <v>61791</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="9" t="n">
         <v>66085</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="9" t="n">
         <v>64180</v>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="L25" s="9" t="n">
         <v>66576</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="M25" s="9" t="n">
         <v>70945</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="9" t="n">
         <v>82584</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="O25" s="9" t="n">
         <v>90525</v>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P25" s="9" t="inlineStr">
         <is>
           <t>237.0%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1797,127 +1845,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ESTOQUE DE EMPREGOS FORMAIS POR SEÇÃO CNAE — CAPANEMA — 2001 A 2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Vínculos empregatícios ativos em 31/12. Fonte: RAIS/MTE — microdados de vínculos (2001-2005: CNAE 95 convertido via tabela de correspondência oficial IBGE; 2007+: CNAE 2.0 direto).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2001</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2003</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2005</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2007</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2009</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2011</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2013</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2015</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2017</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2019</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2021</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2023</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2025</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Δ% acum.
 2001→2025</t>
@@ -1925,1177 +1973,1182 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>614</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>1357</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>1869</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="7" t="n">
         <v>1486</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7" t="n">
         <v>1451</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="7" t="n">
         <v>1122</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="7" t="n">
         <v>1059</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="7" t="n">
         <v>865</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="7" t="n">
         <v>1074</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="7" t="n">
         <v>1269</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="7" t="n">
         <v>1384</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>964.6%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>1214</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>1216</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>1745</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>774</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="7" t="n">
         <v>590</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="7" t="n">
         <v>605</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="7" t="n">
         <v>534</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="7" t="n">
         <v>482</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="7" t="n">
         <v>395</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="7" t="n">
         <v>453</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="7" t="n">
         <v>512</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="7" t="n">
         <v>463</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="7" t="n">
         <v>449</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>-63.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="K7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>-33.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="9" t="n">
         <v>81</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>8000.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>310</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>393</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>555</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>581</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>648</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>857</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>1243</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="7" t="n">
         <v>1229</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="7" t="n">
         <v>1222</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="7" t="n">
         <v>1150</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="7" t="n">
         <v>1500</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="7" t="n">
         <v>1529</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="7" t="n">
         <v>1595</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>414.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="9" t="n">
         <v>179</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>991.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>86</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>1925.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="9" t="inlineStr">
         <is>
           <t>460.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>523.1%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="C15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>300.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>900.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="9" t="n">
         <v>535</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="9" t="n">
         <v>119</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="9" t="n">
         <v>188</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="9" t="n">
         <v>147</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>2840.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>483</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="7" t="n">
         <v>1122</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="7" t="n">
         <v>1362</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="7" t="n">
         <v>1159</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="7" t="n">
         <v>1594</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="7" t="n">
         <v>1481</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="7" t="n">
         <v>1834</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="7" t="n">
         <v>1658</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="7" t="n">
         <v>1594</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="7" t="n">
         <v>1299</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="7" t="n">
         <v>1373</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="7" t="n">
         <v>1786</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="7" t="n">
         <v>1759</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>264.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="9" t="n">
         <v>107</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="9" t="inlineStr">
         <is>
           <t>723.1%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>108.7%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="F21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="9" t="inlineStr">
         <is>
           <t>700.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>633.3%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="C23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="F23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
         <is>
           <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n">
         <v>2229</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="7" t="n">
         <v>4020</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="7" t="n">
         <v>5236</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="7" t="n">
         <v>4623</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G24" s="7" t="n">
         <v>4614</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="7" t="n">
         <v>4813</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="7" t="n">
         <v>5189</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="7" t="n">
         <v>5060</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K24" s="7" t="n">
         <v>4870</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="L24" s="7" t="n">
         <v>4255</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="M24" s="7" t="n">
         <v>5152</v>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N24" s="7" t="n">
         <v>5983</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="O24" s="7" t="n">
         <v>6175</v>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>177.0%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3110,127 +3163,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>ESTOQUE DE EMPREGOS FORMAIS POR SEÇÃO CNAE — PARÁ — 2001 A 2025</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Vínculos empregatícios ativos em 31/12. Fonte: RAIS/MTE — microdados de vínculos (2001-2005: CNAE 95 convertido via tabela de correspondência oficial IBGE; 2007+: CNAE 2.0 direto).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2001</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2003</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2005</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2007</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2009</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2011</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2013</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2015</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2017</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2019</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2021</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2023</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Empregos
 2025</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>Δ% acum.
 2001→2025</t>
@@ -3238,1233 +3291,1238 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>15700</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>24505</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>31559</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>40359</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="7" t="n">
         <v>40108</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="7" t="n">
         <v>49499</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="7" t="n">
         <v>53537</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="7" t="n">
         <v>53272</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="7" t="n">
         <v>52827</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="7" t="n">
         <v>95899</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="7" t="n">
         <v>104645</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="7" t="n">
         <v>128696</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="7" t="n">
         <v>125459</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>699.1%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="9" t="n">
         <v>2912</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="9" t="n">
         <v>4170</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="9" t="n">
         <v>5494</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>9221</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="9" t="n">
         <v>11134</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="9" t="n">
         <v>15483</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="9" t="n">
         <v>19236</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="9" t="n">
         <v>20301</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="9" t="n">
         <v>19710</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="9" t="n">
         <v>26588</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="9" t="n">
         <v>31036</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="9" t="n">
         <v>32326</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="9" t="n">
         <v>35235</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>1110.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>56743</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>71523</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>85855</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>62903</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="7" t="n">
         <v>63372</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="7" t="n">
         <v>67635</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="7" t="n">
         <v>70179</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="7" t="n">
         <v>71266</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="7" t="n">
         <v>68968</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="7" t="n">
         <v>226791</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="7" t="n">
         <v>254796</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="7" t="n">
         <v>293290</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="7" t="n">
         <v>329126</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>480.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="9" t="n">
         <v>3002</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="9" t="n">
         <v>3132</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>2565</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="9" t="n">
         <v>2237</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="9" t="n">
         <v>2670</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="9" t="n">
         <v>2954</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="9" t="n">
         <v>3065</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="9" t="n">
         <v>2637</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="9" t="n">
         <v>12480</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="9" t="n">
         <v>12269</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="9" t="n">
         <v>12380</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="9" t="n">
         <v>13466</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>448766.7%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>2674</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>3124</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>2093</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3966</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="7" t="n">
         <v>5900</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="7" t="n">
         <v>4481</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="7" t="n">
         <v>5364</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="7" t="n">
         <v>5494</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="7" t="n">
         <v>5530</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="7" t="n">
         <v>15304</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="7" t="n">
         <v>17605</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="7" t="n">
         <v>20864</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="7" t="n">
         <v>23938</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>795.2%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>27847</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="9" t="n">
         <v>22406</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="9" t="n">
         <v>30756</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>45945</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="9" t="n">
         <v>53491</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>79913</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="9" t="n">
         <v>109142</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="9" t="n">
         <v>92015</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="9" t="n">
         <v>59704</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="9" t="n">
         <v>109450</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="9" t="n">
         <v>133233</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="9" t="n">
         <v>171073</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="9" t="n">
         <v>176738</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>534.7%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="7" t="n">
         <v>75667</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="7" t="n">
         <v>94699</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="7" t="n">
         <v>118811</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>134623</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="7" t="n">
         <v>151999</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="7" t="n">
         <v>182830</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="7" t="n">
         <v>207469</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="7" t="n">
         <v>212462</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="7" t="n">
         <v>198650</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="7" t="n">
         <v>497477</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="7" t="n">
         <v>542768</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="7" t="n">
         <v>612336</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="7" t="n">
         <v>661411</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>774.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="9" t="n">
         <v>21450</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="9" t="n">
         <v>22226</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="9" t="n">
         <v>25504</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>29105</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="9" t="n">
         <v>32223</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="9" t="n">
         <v>39246</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="9" t="n">
         <v>41401</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="9" t="n">
         <v>44598</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="9" t="n">
         <v>42030</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="9" t="n">
         <v>103640</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="9" t="n">
         <v>110203</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="9" t="n">
         <v>128750</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="9" t="n">
         <v>141324</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>558.9%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>6594</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>11143</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="7" t="n">
         <v>12812</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>16129</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="7" t="n">
         <v>19452</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="7" t="n">
         <v>23719</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="7" t="n">
         <v>27599</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="7" t="n">
         <v>28328</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="7" t="n">
         <v>24480</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="7" t="n">
         <v>67976</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="7" t="n">
         <v>66729</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="7" t="n">
         <v>90186</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="7" t="n">
         <v>105488</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>1499.8%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="9" t="n">
         <v>5155</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="9" t="n">
         <v>5088</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="9" t="n">
         <v>5945</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="9" t="n">
         <v>5476</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="9" t="n">
         <v>5040</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="9" t="n">
         <v>6280</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="9" t="n">
         <v>7154</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="9" t="n">
         <v>8598</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="9" t="n">
         <v>10057</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="9" t="n">
         <v>25964</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="9" t="n">
         <v>29157</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="9" t="n">
         <v>36496</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="9" t="n">
         <v>41282</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="9" t="inlineStr">
         <is>
           <t>700.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="7" t="n">
         <v>7078</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="7" t="n">
         <v>7647</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="7" t="n">
         <v>8625</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="7" t="n">
         <v>8604</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="7" t="n">
         <v>11025</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="7" t="n">
         <v>11550</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="7" t="n">
         <v>12481</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="7" t="n">
         <v>13254</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" s="7" t="n">
         <v>13243</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="7" t="n">
         <v>30199</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="7" t="n">
         <v>34536</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="7" t="n">
         <v>38846</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="7" t="n">
         <v>38374</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>442.2%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="9" t="n">
         <v>459</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="9" t="n">
         <v>626</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="9" t="n">
         <v>777</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="9" t="n">
         <v>613</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="9" t="n">
         <v>916</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="9" t="n">
         <v>1943</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="9" t="n">
         <v>2572</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="9" t="n">
         <v>2135</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="9" t="n">
         <v>2173</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="9" t="n">
         <v>5247</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="9" t="n">
         <v>6374</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="9" t="n">
         <v>8098</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="9" t="n">
         <v>7575</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>1550.3%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="7" t="n">
         <v>5278</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="7" t="n">
         <v>5964</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="7" t="n">
         <v>7176</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="7" t="n">
         <v>9905</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="7" t="n">
         <v>11913</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="7" t="n">
         <v>14506</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="7" t="n">
         <v>16155</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="7" t="n">
         <v>15922</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="7" t="n">
         <v>16267</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="7" t="n">
         <v>44049</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="7" t="n">
         <v>53364</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="7" t="n">
         <v>74327</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="7" t="n">
         <v>83276</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>1477.8%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="9" t="n">
         <v>28275</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="9" t="n">
         <v>31450</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="9" t="n">
         <v>38054</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="9" t="n">
         <v>40151</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="9" t="n">
         <v>44968</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="9" t="n">
         <v>62712</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="9" t="n">
         <v>64323</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="9" t="n">
         <v>62529</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="9" t="n">
         <v>63524</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="9" t="n">
         <v>181145</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="9" t="n">
         <v>204067</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="9" t="n">
         <v>271729</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="9" t="n">
         <v>318164</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>1025.2%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>173742</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="7" t="n">
         <v>215686</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="7" t="n">
         <v>248166</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="7" t="n">
         <v>244221</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="7" t="n">
         <v>326280</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="7" t="n">
         <v>373338</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="7" t="n">
         <v>377320</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="7" t="n">
         <v>373752</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="7" t="n">
         <v>367432</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="7" t="n">
         <v>953930</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="7" t="n">
         <v>954256</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="7" t="n">
         <v>1071078</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="7" t="n">
         <v>1342078</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>672.5%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>12696</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="9" t="n">
         <v>14441</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="9" t="n">
         <v>22039</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="9" t="n">
         <v>20773</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="9" t="n">
         <v>28600</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="9" t="n">
         <v>34725</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="9" t="n">
         <v>41494</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="9" t="n">
         <v>44615</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19" s="9" t="n">
         <v>109266</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="9" t="n">
         <v>93748</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="9" t="n">
         <v>225242</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="9" t="n">
         <v>220279</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="9" t="inlineStr">
         <is>
           <t>1635.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="7" t="n">
         <v>16331</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="7" t="n">
         <v>16299</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="7" t="n">
         <v>17384</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="7" t="n">
         <v>18864</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="7" t="n">
         <v>22041</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="7" t="n">
         <v>26072</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="7" t="n">
         <v>31019</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="7" t="n">
         <v>37306</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="7" t="n">
         <v>41836</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="7" t="n">
         <v>92048</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="7" t="n">
         <v>108140</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="7" t="n">
         <v>147897</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="7" t="n">
         <v>168505</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>931.8%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="9" t="n">
         <v>2616</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="9" t="n">
         <v>2617</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="9" t="n">
         <v>2679</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="9" t="n">
         <v>2897</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="9" t="n">
         <v>3280</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="9" t="n">
         <v>3977</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="9" t="n">
         <v>3871</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="9" t="n">
         <v>5235</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="9" t="n">
         <v>4992</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="9" t="n">
         <v>9032</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="9" t="n">
         <v>8562</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="9" t="n">
         <v>13586</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="9" t="n">
         <v>17498</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="9" t="inlineStr">
         <is>
           <t>568.9%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>15157</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="7" t="n">
         <v>16874</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="7" t="n">
         <v>15790</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="7" t="n">
         <v>15700</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="7" t="n">
         <v>15908</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="7" t="n">
         <v>17598</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="7" t="n">
         <v>17832</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="7" t="n">
         <v>19552</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="7" t="n">
         <v>18187</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="7" t="n">
         <v>42594</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="7" t="n">
         <v>43068</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="7" t="n">
         <v>59093</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="7" t="n">
         <v>61678</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>306.9%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="9" t="n">
         <v>79</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="9" t="n">
         <v>123</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="9" t="n">
         <v>160</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="9" t="n">
         <v>156</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="9" t="n">
         <v>191</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="9" t="n">
         <v>178</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="9" t="n">
         <v>82</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="9" t="n">
         <v>159</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="9" t="n">
         <v>123</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="9" t="inlineStr">
         <is>
           <t>-59.5%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="7" t="n">
         <v>151</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>485.7%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
         <v>463767</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="9" t="n">
         <v>571905</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="9" t="n">
         <v>675223</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="9" t="n">
         <v>713451</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="9" t="n">
         <v>842271</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="9" t="n">
         <v>1012381</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="9" t="n">
         <v>1104452</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="9" t="n">
         <v>1110678</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K25" s="9" t="n">
         <v>1056939</v>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="L25" s="9" t="n">
         <v>2649286</v>
       </c>
-      <c r="M25" s="2" t="n">
+      <c r="M25" s="9" t="n">
         <v>2808709</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="9" t="n">
         <v>3436357</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="O25" s="9" t="n">
         <v>3910967</v>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P25" s="9" t="inlineStr">
         <is>
           <t>743.3%</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>